--- a/Project3646_I. Orlov(2021).xlsx
+++ b/Project3646_I. Orlov(2021).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjjg18\GitHub\neotrans\matrices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjjg18\GitHub\neotrans\inst\matrices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D0FB1B-905E-4892-AECC-67F26936B3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA8CC0F-8D30-44E2-9830-A0C3A0EAE081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16455" yWindow="2340" windowWidth="15945" windowHeight="18375" xr2:uid="{77F1F6C2-35A7-D941-8ED6-BBEDF1D994A1}"/>
+    <workbookView xWindow="16290" yWindow="1560" windowWidth="16110" windowHeight="17460" xr2:uid="{77F1F6C2-35A7-D941-8ED6-BBEDF1D994A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Project3646" sheetId="1" r:id="rId1"/>
@@ -659,9 +659,6 @@
     <t>NO</t>
   </si>
   <si>
-    <t>Tranformational</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
@@ -681,6 +678,9 @@
   </si>
   <si>
     <t>NT?;0=11;1=0-;2=12</t>
+  </si>
+  <si>
+    <t>Transformational</t>
   </si>
 </sst>
 </file>
@@ -1099,10 +1099,10 @@
         <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1121,7 +1121,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>206</v>
@@ -1132,10 +1132,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1154,7 +1154,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>206</v>
@@ -1165,7 +1165,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>206</v>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>206</v>
@@ -1231,7 +1231,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>206</v>
@@ -1242,7 +1242,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>206</v>
@@ -1253,7 +1253,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>206</v>
@@ -1264,7 +1264,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>206</v>
@@ -1275,10 +1275,10 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1297,7 +1297,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>206</v>
@@ -1308,7 +1308,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>206</v>
@@ -1319,7 +1319,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>206</v>
@@ -1330,7 +1330,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1338,7 +1338,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1357,10 +1357,10 @@
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1368,7 +1368,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C27" s="3"/>
     </row>
@@ -1377,10 +1377,10 @@
         <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1399,10 +1399,10 @@
         <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1410,10 +1410,10 @@
         <v>31</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1432,7 +1432,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>206</v>
@@ -1454,7 +1454,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>206</v>
@@ -1465,7 +1465,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>206</v>
@@ -1487,7 +1487,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>206</v>
@@ -1509,7 +1509,7 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>206</v>
@@ -1531,10 +1531,10 @@
         <v>42</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1542,10 +1542,10 @@
         <v>43</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1564,7 +1564,7 @@
         <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>206</v>
@@ -1575,10 +1575,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1608,10 +1608,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1619,7 +1619,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>206</v>
@@ -1641,10 +1641,10 @@
         <v>52</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1663,10 +1663,10 @@
         <v>54</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1674,7 +1674,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>206</v>
@@ -1718,7 +1718,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>206</v>
@@ -1751,7 +1751,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>206</v>
@@ -1762,7 +1762,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>206</v>
@@ -1773,7 +1773,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>206</v>
@@ -1784,10 +1784,10 @@
         <v>65</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C65" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1795,10 +1795,10 @@
         <v>66</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C66" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1806,10 +1806,10 @@
         <v>67</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C67" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1817,10 +1817,10 @@
         <v>68</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C68" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1839,10 +1839,10 @@
         <v>70</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -1861,10 +1861,10 @@
         <v>72</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1872,10 +1872,10 @@
         <v>73</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C73" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1883,7 +1883,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>206</v>
@@ -1894,7 +1894,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1902,7 +1902,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>206</v>
@@ -1913,10 +1913,10 @@
         <v>77</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C77" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1924,10 +1924,10 @@
         <v>78</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C78" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -1946,10 +1946,10 @@
         <v>80</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C80" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1957,10 +1957,10 @@
         <v>81</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C81" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1968,10 +1968,10 @@
         <v>82</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C82" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1979,7 +1979,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>206</v>
@@ -1990,7 +1990,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>206</v>
@@ -2001,7 +2001,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>206</v>
@@ -2012,10 +2012,10 @@
         <v>86</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C86" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2023,7 +2023,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>206</v>
@@ -2034,10 +2034,10 @@
         <v>88</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C88" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2045,10 +2045,10 @@
         <v>89</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C89" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2056,7 +2056,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>206</v>
@@ -2078,7 +2078,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>206</v>
@@ -2089,7 +2089,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>206</v>
@@ -2100,7 +2100,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2108,10 +2108,10 @@
         <v>95</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C95" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2119,7 +2119,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>206</v>
@@ -2152,7 +2152,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2160,10 +2160,10 @@
         <v>100</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C100" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2171,10 +2171,10 @@
         <v>101</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2182,7 +2182,7 @@
         <v>102</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>206</v>
@@ -2193,10 +2193,10 @@
         <v>103</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2204,7 +2204,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2212,7 +2212,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2231,7 +2231,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2239,7 +2239,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>206</v>
@@ -2250,10 +2250,10 @@
         <v>109</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -2272,10 +2272,10 @@
         <v>111</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2283,10 +2283,10 @@
         <v>112</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -2305,7 +2305,7 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>206</v>
@@ -2327,10 +2327,10 @@
         <v>116</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -2338,7 +2338,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>206</v>
@@ -2349,10 +2349,10 @@
         <v>118</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -2382,10 +2382,10 @@
         <v>121</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -2393,10 +2393,10 @@
         <v>122</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>206</v>
@@ -2415,10 +2415,10 @@
         <v>124</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -2448,7 +2448,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2467,10 +2467,10 @@
         <v>129</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2500,7 +2500,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -2519,10 +2519,10 @@
         <v>134</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -2530,7 +2530,7 @@
         <v>135</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -2538,10 +2538,10 @@
         <v>136</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -2549,10 +2549,10 @@
         <v>137</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -2571,10 +2571,10 @@
         <v>139</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -2582,10 +2582,10 @@
         <v>140</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -2593,7 +2593,7 @@
         <v>141</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>206</v>
@@ -2604,7 +2604,7 @@
         <v>142</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -2612,7 +2612,7 @@
         <v>143</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -2620,7 +2620,7 @@
         <v>144</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>206</v>
@@ -2631,7 +2631,7 @@
         <v>145</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>206</v>
@@ -2642,10 +2642,10 @@
         <v>146</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -2653,7 +2653,7 @@
         <v>147</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>206</v>
@@ -2675,7 +2675,7 @@
         <v>149</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>206</v>
@@ -2686,7 +2686,7 @@
         <v>150</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>206</v>
@@ -2708,10 +2708,10 @@
         <v>152</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -2719,10 +2719,10 @@
         <v>153</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -2741,7 +2741,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -2771,10 +2771,10 @@
         <v>158</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -2782,10 +2782,10 @@
         <v>159</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -2793,7 +2793,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -2801,10 +2801,10 @@
         <v>161</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -2823,10 +2823,10 @@
         <v>163</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -2845,10 +2845,10 @@
         <v>165</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -2856,7 +2856,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>206</v>
@@ -2867,7 +2867,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>206</v>
@@ -2889,10 +2889,10 @@
         <v>169</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -2922,10 +2922,10 @@
         <v>172</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -2933,7 +2933,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>206</v>
@@ -2944,10 +2944,10 @@
         <v>174</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -2955,7 +2955,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>206</v>
@@ -2966,10 +2966,10 @@
         <v>176</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -2988,10 +2988,10 @@
         <v>178</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3010,7 +3010,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>206</v>
@@ -3021,10 +3021,10 @@
         <v>181</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -3032,10 +3032,10 @@
         <v>182</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -3043,7 +3043,7 @@
         <v>183</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>206</v>
@@ -3065,10 +3065,10 @@
         <v>185</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -3109,10 +3109,10 @@
         <v>189</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -3120,7 +3120,7 @@
         <v>190</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>206</v>
@@ -3153,10 +3153,10 @@
         <v>193</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -3164,7 +3164,7 @@
         <v>194</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>206</v>
@@ -3175,7 +3175,7 @@
         <v>195</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>206</v>
@@ -3186,7 +3186,7 @@
         <v>196</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>206</v>
@@ -3197,7 +3197,7 @@
         <v>197</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -3205,10 +3205,10 @@
         <v>198</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -3216,7 +3216,7 @@
         <v>199</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -3235,7 +3235,7 @@
         <v>201</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -3243,7 +3243,7 @@
         <v>202</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>206</v>
@@ -3254,7 +3254,7 @@
         <v>203</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
